--- a/sheet1.xlsx
+++ b/sheet1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\finjun\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCB1E71-1714-49E4-9B7B-32B3959FC8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C818396-7A64-4A52-B408-98D3D0EC1FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45760" yWindow="2580" windowWidth="28800" windowHeight="15480" xr2:uid="{E846A769-CBA6-4B93-854B-74D22F1427FD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{E846A769-CBA6-4B93-854B-74D22F1427FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
